--- a/backend/python/templates/FAAS_Template_WithoutEntry2.xlsx
+++ b/backend/python/templates/FAAS_Template_WithoutEntry2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Videos\FAAS SYSTEM\backend\python\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\FAAS-System\backend\python\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402F0140-1DD4-4011-9B53-7D49CF5485FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADEAF6C-2835-4187-B9B1-4D4E238878C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,9 +180,6 @@
     <t>Approved by:</t>
   </si>
   <si>
-    <t>RICARDO J. NIEVA</t>
-  </si>
-  <si>
     <t>REENA N. AURIN  REA-0005811</t>
   </si>
   <si>
@@ -217,6 +214,9 @@
   </si>
   <si>
     <t>Previous Total AV:</t>
+  </si>
+  <si>
+    <t>RICARDO J. NIEVA REA-0000483</t>
   </si>
 </sst>
 </file>
@@ -638,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -666,7 +666,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -733,10 +732,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -745,6 +740,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -777,26 +780,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1232,28 +1231,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1276,463 +1275,463 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="30"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="30"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="29"/>
       <c r="E6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="30"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="30"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="30"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="57" t="s">
+      <c r="B8" s="52"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="55"/>
     </row>
     <row r="9" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="58"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="56"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="57"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="57" t="s">
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="53"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="55"/>
     </row>
     <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="58"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="56"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="57"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="30"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="30"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="30"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="30"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="30"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="30"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="30"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="30"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="30"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="30"/>
+      <c r="B21" s="29"/>
       <c r="C21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="29" t="s">
+      <c r="F21" s="29"/>
+      <c r="G21" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="30"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="29"/>
       <c r="C22" s="13"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="30"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="24"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="14"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="30"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="14"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="30"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="29"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="23"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="22"/>
       <c r="D25" s="14"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="30"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="30"/>
+      <c r="B26" s="29"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="35" t="str">
+      <c r="E26" s="28"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="34" t="str">
         <f>IF(SUM(G22:H25)=0, "", SUM(G22:H25))</f>
         <v/>
       </c>
-      <c r="H26" s="30"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="30"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="29" t="s">
+      <c r="B28" s="29"/>
+      <c r="C28" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="30"/>
-      <c r="E28" s="29" t="s">
+      <c r="D28" s="29"/>
+      <c r="E28" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="29" t="s">
+      <c r="F28" s="29"/>
+      <c r="G28" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="H28" s="30"/>
+      <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="31"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="30"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="30"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="30"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="30"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="29"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="35" t="str">
+      <c r="B33" s="29"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="34" t="str">
         <f>IF(SUM(G29:H32)=0, "", SUM(G29:H32))</f>
         <v/>
       </c>
-      <c r="H33" s="30"/>
+      <c r="H33" s="29"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="44" t="s">
+      <c r="A34" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="30"/>
+      <c r="B35" s="29"/>
       <c r="C35" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="29" t="s">
+      <c r="F35" s="29"/>
+      <c r="G35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="30"/>
+      <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="30"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="29"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="30"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="29"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="30"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="29"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="47"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="44"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="30"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="35" t="str">
+      <c r="E40" s="28"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="34" t="str">
         <f>IF(SUM(G36:H39)=0, "", SUM(G36:H39))</f>
         <v/>
       </c>
-      <c r="H40" s="30"/>
+      <c r="H40" s="29"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="30"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="29"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
@@ -1741,73 +1740,73 @@
       <c r="B42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="29" t="s">
+      <c r="D42" s="29"/>
+      <c r="E42" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="F42" s="30"/>
-      <c r="G42" s="29" t="s">
+      <c r="F42" s="29"/>
+      <c r="G42" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H42" s="30"/>
+      <c r="H42" s="29"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="30"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="30"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="29"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="30"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="29"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="23"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="30"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="29"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="15"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="29"/>
       <c r="E47" s="6"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="35" t="str">
+      <c r="G47" s="34" t="str">
         <f>IF(SUM(G43:H46)=0, "", SUM(G43:H46))</f>
         <v/>
       </c>
-      <c r="H47" s="30"/>
+      <c r="H47" s="29"/>
     </row>
     <row r="48" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
@@ -1828,54 +1827,54 @@
       <c r="A50" s="9"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="43"/>
-      <c r="B51" s="41"/>
-      <c r="D51" s="44" t="s">
+      <c r="A51" s="42"/>
+      <c r="B51" s="40"/>
+      <c r="D51" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="E51" s="45"/>
+      <c r="E51" s="48"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="44" t="s">
+      <c r="G51" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="H51" s="45"/>
+      <c r="H51" s="48"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="39"/>
-      <c r="D52" s="32" t="s">
+      <c r="B52" s="38"/>
+      <c r="D52" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="33"/>
-      <c r="G52" s="32" t="s">
+      <c r="E52" s="32"/>
+      <c r="G52" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="H52" s="33"/>
+      <c r="H52" s="32"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="18"/>
+      <c r="A53" s="17"/>
       <c r="E53" s="9"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="50" t="s">
+      <c r="D54" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="E54" s="28"/>
+      <c r="E54" s="27"/>
       <c r="F54" s="9"/>
-      <c r="G54" s="50" t="s">
+      <c r="G54" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="H54" s="28"/>
+      <c r="H54" s="27"/>
     </row>
     <row r="55" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
@@ -1883,146 +1882,146 @@
     <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="48"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="E56" s="45"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="43" t="s">
+      <c r="H56" s="40"/>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D57" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="H56" s="41"/>
-    </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D57" s="32" t="s">
+      <c r="E57" s="32"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="33"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="H57" s="28"/>
+      <c r="H57" s="27"/>
     </row>
     <row r="58" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="59"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
+        <v>51</v>
+      </c>
+      <c r="B59" s="60"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
     </row>
     <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="68"/>
-      <c r="B60" s="39"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="40"/>
+      <c r="A60" s="70"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="39"/>
     </row>
     <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="69"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="70"/>
+      <c r="A61" s="71"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="72"/>
     </row>
     <row r="62" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="52"/>
-      <c r="B62" s="41"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="42"/>
+      <c r="A62" s="53"/>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="41"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="10"/>
       <c r="F63" s="10"/>
-      <c r="H63" s="16"/>
+      <c r="H63" s="15"/>
     </row>
     <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="21" t="s">
+      <c r="A64" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" s="49"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B64" s="64"/>
-      <c r="C64" s="49"/>
-      <c r="D64" s="20" t="s">
+      <c r="E64" s="22"/>
+      <c r="F64" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="E64" s="23"/>
-      <c r="F64" s="48" t="s">
+      <c r="G64" s="46"/>
+      <c r="H64" s="25"/>
+    </row>
+    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="G64" s="49"/>
-      <c r="H64" s="26"/>
-    </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="67" t="s">
+      <c r="B65" s="67"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="B65" s="71"/>
-      <c r="C65" s="72"/>
-      <c r="D65" s="67" t="s">
+      <c r="E65" s="49"/>
+      <c r="F65" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="E65" s="64"/>
-      <c r="F65" s="48" t="s">
+      <c r="G65" s="46"/>
+      <c r="H65" s="25"/>
+    </row>
+    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="50"/>
+      <c r="B66" s="69"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="G65" s="49"/>
-      <c r="H65" s="26"/>
-    </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="65"/>
-      <c r="B66" s="73"/>
-      <c r="C66" s="56"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="G66" s="49"/>
-      <c r="H66" s="26" t="str">
+      <c r="G66" s="46"/>
+      <c r="H66" s="25" t="str">
         <f>IF(SUM(H64:H65)=0, "", MROUND(SUM(H64:H65), 10))</f>
         <v/>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
     </row>
     <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="28"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
+      <c r="A68" s="27"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
     </row>
     <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="28"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
+      <c r="A69" s="27"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="134">
+  <mergeCells count="135">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="F64:G64"/>
@@ -2038,6 +2037,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="F66:G66"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C47:D47"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="A22:B22"/>
@@ -2110,10 +2114,6 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="F14:H14"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="B68:C69"/>
     <mergeCell ref="F68:G68"/>
     <mergeCell ref="G52:H52"/>
